--- a/input/api_definition.xlsx
+++ b/input/api_definition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="363">
   <si>
     <t>API定義一覧</t>
   </si>
@@ -477,6 +477,27 @@
   </si>
   <si>
     <t>全 API に付けるヘッダ。「名前: 値」を改行区切り</t>
+  </si>
+  <si>
+    <t>access_token_dir</t>
+  </si>
+  <si>
+    <t>アクセストークンのフォルダ</t>
+  </si>
+  <si>
+    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス。-JACCESS_TOKEN_DIR</t>
+  </si>
+  <si>
+    <t>access_token_file</t>
+  </si>
+  <si>
+    <t>アクセストークンのファイル名</t>
+  </si>
+  <si>
+    <t>access_token.txt</t>
+  </si>
+  <si>
+    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
   </si>
   <si>
     <t>follow_redirects</t>
@@ -2296,7 +2317,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2619,35 +2640,33 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="46.8" customHeight="1">
       <c r="A22" s="22" t="s">
         <v>146</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="23"/>
+      <c r="D22" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" s="14" t="s">
+    </row>
+    <row r="23" ht="32.4" customHeight="1">
+      <c r="A23" s="22" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="B23" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="C23" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>148</v>
-      </c>
       <c r="D23" s="22" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>152</v>
@@ -2670,61 +2689,61 @@
         <v>156</v>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="21" t="s">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
+      <c r="B25" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="22" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="14" t="s">
         <v>163</v>
       </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>167</v>
@@ -2737,58 +2756,58 @@
       <c r="B29" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="23"/>
+      <c r="C29" s="23" t="s">
+        <v>155</v>
+      </c>
       <c r="D29" s="22" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="21" t="s">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" ht="32.4" customHeight="1">
+      <c r="B30" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
       <c r="A31" s="22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>174</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="C31" s="23"/>
       <c r="D31" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="B32" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E32" s="14" t="s">
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="21" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+    </row>
+    <row r="33" ht="32.4" customHeight="1">
       <c r="A33" s="22" t="s">
         <v>179</v>
       </c>
@@ -2799,7 +2818,7 @@
         <v>181</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>182</v>
@@ -2813,74 +2832,74 @@
         <v>184</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="14"/>
+        <v>188</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>190</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E36" s="14"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>194</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E37" s="14"/>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="C38" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="C38" s="23" t="s">
-        <v>132</v>
-      </c>
       <c r="D38" s="22" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>197</v>
@@ -2899,80 +2918,80 @@
       <c r="D39" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="E39" s="14"/>
+      <c r="E39" s="14" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="14"/>
+        <v>132</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="22" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E41" s="14"/>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="14"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="22" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="44" ht="32.4" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C44" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="D44" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="E44" s="14" t="s">
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="21" t="s">
         <v>213</v>
       </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="22" t="s">
@@ -2981,15 +3000,17 @@
       <c r="B45" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C45" s="23"/>
+      <c r="C45" s="23" t="s">
+        <v>132</v>
+      </c>
       <c r="D45" s="22" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="32.4" customHeight="1">
       <c r="A46" s="22" t="s">
         <v>217</v>
       </c>
@@ -2997,121 +3018,119 @@
         <v>218</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E46" s="14"/>
+        <v>219</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>221</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C47" s="23"/>
       <c r="D47" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="E47" s="14"/>
+        <v>98</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>224</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E48" s="14"/>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>227</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="E49" s="14"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="21" t="s">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
+      <c r="B51" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="22" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="53" ht="32.4" customHeight="1">
-      <c r="A53" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="B53" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="E53" s="14" t="s">
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="21" t="s">
         <v>239</v>
       </c>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="22" t="s">
@@ -3120,63 +3139,63 @@
       <c r="B54" s="22" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="23"/>
+      <c r="C54" s="23" t="s">
+        <v>132</v>
+      </c>
       <c r="D54" s="22" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="21" t="s">
+    <row r="55" ht="32.4" customHeight="1">
+      <c r="A55" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
+      <c r="B55" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>132</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C56" s="23"/>
       <c r="D56" s="22" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="57" ht="32.4" customHeight="1">
-      <c r="A57" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D57" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" s="14" t="s">
         <v>249</v>
       </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C58" s="23" t="s">
         <v>132</v>
@@ -3185,51 +3204,51 @@
         <v>132</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="B59" s="21"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
+    </row>
+    <row r="59" ht="32.4" customHeight="1">
+      <c r="A59" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="B61" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="C61" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="D61" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" s="14" t="s">
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="21" t="s">
         <v>260</v>
       </c>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="22" t="s">
@@ -3239,21 +3258,21 @@
         <v>262</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C63" s="23" t="s">
         <v>132</v>
@@ -3262,15 +3281,15 @@
         <v>132</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C64" s="23" t="s">
         <v>132</v>
@@ -3279,15 +3298,15 @@
         <v>132</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="22" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C65" s="23" t="s">
         <v>132</v>
@@ -3296,15 +3315,15 @@
         <v>132</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="23" t="s">
         <v>132</v>
@@ -3313,21 +3332,21 @@
         <v>132</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>278</v>
+        <v>132</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>278</v>
+        <v>132</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>279</v>
@@ -3341,10 +3360,10 @@
         <v>281</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>282</v>
@@ -3358,13 +3377,47 @@
         <v>284</v>
       </c>
       <c r="C69" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" s="14" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C71" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="D69" s="22" t="s">
+      <c r="D71" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E69" s="14" t="s">
-        <v>285</v>
+      <c r="E71" s="14" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3374,12 +3427,12 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A61:E61"/>
   </mergeCells>
   <dataValidations count="26">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C14">
@@ -3391,55 +3444,49 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C18">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C22">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C24">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C23">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C25">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C26">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C28">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C27">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C29">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C32">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C34">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C37">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C39">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C38">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C40">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C43">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C45">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C48">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C50">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C49">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C51">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C50">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C52">
       <formula1>"all,group,thread"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C52">
-      <formula1>"ON,OFF,DISABLE"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C56">
-      <formula1>"ON,OFF,DISABLE"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C57">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C54">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C58">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C61">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C59">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C62">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C60">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C63">
@@ -3455,9 +3502,15 @@
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C67">
+      <formula1>"ON,OFF,DISABLE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C68">
+      <formula1>"ON,OFF,DISABLE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C69">
       <formula1>"none,error,all"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C69">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="C71">
       <formula1>"ON,OFF,DISABLE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3486,7 +3539,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3495,7 +3548,7 @@
     <row r="2" ht="6" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -3504,7 +3557,7 @@
     <row r="4" ht="4" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="7" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -3512,7 +3565,7 @@
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -3520,7 +3573,7 @@
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="B7" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -3529,7 +3582,7 @@
     <row r="8" ht="6" customHeight="1"/>
     <row r="9" ht="16.2" customHeight="1">
       <c r="B9" s="9" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -3537,7 +3590,7 @@
     </row>
     <row r="10" ht="16.2" customHeight="1">
       <c r="B10" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -3547,7 +3600,7 @@
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="4" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -3556,7 +3609,7 @@
     <row r="14" ht="4" customHeight="1"/>
     <row r="15" ht="18" customHeight="1">
       <c r="B15" s="7" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -3564,7 +3617,7 @@
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -3572,7 +3625,7 @@
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="7" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -3580,7 +3633,7 @@
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="B18" s="7" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -3588,7 +3641,7 @@
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="B19" s="7" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -3596,7 +3649,7 @@
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="B20" s="7" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -3606,7 +3659,7 @@
     <row r="22" ht="8" customHeight="1"/>
     <row r="23" ht="24" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -3615,16 +3668,16 @@
     <row r="24" ht="4" customHeight="1"/>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="13" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>86</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" ht="32.4" customHeight="1">
@@ -3633,7 +3686,7 @@
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>35</v>
@@ -3645,7 +3698,7 @@
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>36</v>
@@ -3657,10 +3710,10 @@
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -3668,10 +3721,10 @@
         <v>5</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>38</v>
@@ -3682,13 +3735,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" ht="32.4" customHeight="1">
@@ -3697,10 +3750,10 @@
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="15" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -3709,7 +3762,7 @@
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>57</v>
@@ -3721,7 +3774,7 @@
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="15" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>41</v>
@@ -3733,10 +3786,10 @@
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="14" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" ht="32.4" customHeight="1">
@@ -3745,7 +3798,7 @@
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>58</v>
@@ -3757,7 +3810,7 @@
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>44</v>
@@ -3769,10 +3822,10 @@
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="15" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3781,10 +3834,10 @@
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3793,10 +3846,10 @@
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="15" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3805,10 +3858,10 @@
       </c>
       <c r="C40" s="14"/>
       <c r="D40" s="14" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3817,10 +3870,10 @@
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="15" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="42" ht="32.4" customHeight="1">
@@ -3829,10 +3882,10 @@
       </c>
       <c r="C42" s="14"/>
       <c r="D42" s="14" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3841,7 +3894,7 @@
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E43" s="15"/>
     </row>
@@ -3849,7 +3902,7 @@
     <row r="45" ht="8" customHeight="1"/>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="4" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -3858,85 +3911,85 @@
     <row r="47" ht="4" customHeight="1"/>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="13" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E48" s="13"/>
     </row>
     <row r="49" ht="32.4" customHeight="1">
       <c r="B49" s="14" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E49" s="14"/>
     </row>
     <row r="50" ht="32.4" customHeight="1">
       <c r="B50" s="15" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E50" s="15"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="14" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E51" s="14"/>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="15" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E52" s="15"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="14" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E53" s="14"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="15" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E54" s="15"/>
     </row>
@@ -3944,7 +3997,7 @@
     <row r="56" ht="8" customHeight="1"/>
     <row r="57" ht="24" customHeight="1">
       <c r="B57" s="4" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -3953,7 +4006,7 @@
     <row r="58" ht="4" customHeight="1"/>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="7" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -3961,7 +4014,7 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="7" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>

--- a/input/api_definition.xlsx
+++ b/input/api_definition.xlsx
@@ -485,7 +485,7 @@
     <t>アクセストークンのフォルダ</t>
   </si>
   <si>
-    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス。-JACCESS_TOKEN_DIR</t>
+    <t>指定すると、このフォルダ配下のファイルからアクセストークンを読み込み、共通ヘッダに Authorization: Bearer ${ACCESS_TOKEN} を付けます（共通ヘッダに Authorization がある場合はその値を使用）。空欄 = 使わない。JMX からの相対パスまたは絶対パス（区切りは \ と / のどちらでも可。; で区切って複数書くと、存在する最初のフォルダを使用）。-JACCESS_TOKEN_DIR</t>
   </si>
   <si>
     <t>access_token_file</t>
@@ -497,7 +497,7 @@
     <t>access_token.txt</t>
   </si>
   <si>
-    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
+    <t>アクセストークンを書いたファイルの名前（フォルダからの相対パス）。*.token のように * を含めると、一致するファイルのうち更新日時が最も新しいファイルを使います。前後の空白・改行は除き、実行中にファイルが更新されると読み直します。-JACCESS_TOKEN_FILE</t>
   </si>
   <si>
     <t>follow_redirects</t>
@@ -2640,7 +2640,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" ht="46.8" customHeight="1">
+    <row r="22" ht="61.2" customHeight="1">
       <c r="A22" s="22" t="s">
         <v>146</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" ht="32.4" customHeight="1">
+    <row r="23" ht="46.8" customHeight="1">
       <c r="A23" s="22" t="s">
         <v>149</v>
       </c>
